--- a/daughterboard/miata_ecu_daughterboard_parts.xlsx
+++ b/daughterboard/miata_ecu_daughterboard_parts.xlsx
@@ -6592,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7109,399 +7109,463 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>PD12</t>
+          <t>PD8</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>LED_RUN</t>
+          <t>WB_PROG_TX</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>PD13</t>
+          <t>PD9</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>LED_COMM</t>
+          <t>WB_PROG_RX</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>PD14</t>
+          <t>PD10</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>LED_WARN</t>
+          <t>WB_BOOT0</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>PD15</t>
+          <t>PD11</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>LED_ERR</t>
+          <t>WB_NRST</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PD12</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>UART_TX</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>USART3 TX (3.3V, Bluetooth etc.)</t>
-        </is>
-      </c>
+          <t>LED_RUN</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PD13</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>UART_RX</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>USART3 RX</t>
-        </is>
-      </c>
+          <t>LED_COMM</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>PA11</t>
+          <t>PD14</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>USB_DM</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>USB D- to motherboard USB-C</t>
-        </is>
-      </c>
+          <t>LED_WARN</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>PA12</t>
+          <t>PD15</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>USB_DP</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>USB D+</t>
-        </is>
-      </c>
+          <t>LED_ERR</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>PA13</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>SWDIO</t>
+          <t>UART_TX</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>SWD data</t>
+          <t>USART3 TX (3.3V, Bluetooth etc.)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>PA14</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>SWCLK</t>
+          <t>UART_RX</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>SWD clock</t>
+          <t>USART3 RX</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>PD5</t>
+          <t>PA11</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>ALT_CTL</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr"/>
+          <t>USB_DM</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>USB D- to motherboard USB-C</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>PD6</t>
+          <t>PA12</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>BOOST_CTL</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr"/>
+          <t>USB_DP</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>USB D+</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PD7</t>
+          <t>PA13</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>VVT_CTL</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr"/>
+          <t>SWDIO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>SWD data</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>PB3</t>
+          <t>PA14</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>IACV_CTL</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr"/>
+          <t>SWCLK</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>SWD clock</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PD5</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>INJ4_CTL</t>
+          <t>ALT_CTL</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>PB5</t>
+          <t>PD6</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>INJ3_CTL</t>
+          <t>BOOST_CTL</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>PB6</t>
+          <t>PD7</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>INJ2_CTL</t>
+          <t>VVT_CTL</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>PB7</t>
+          <t>PB3</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>INJ1_CTL</t>
+          <t>IACV_CTL</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>BOOT0</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>BOOT0</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>DFU boot select</t>
-        </is>
-      </c>
+          <t>INJ4_CTL</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>PB8</t>
+          <t>PB5</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>IGN4_CTL</t>
+          <t>INJ3_CTL</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>PB9</t>
+          <t>PB6</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>IGN3_CTL</t>
+          <t>INJ2_CTL</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>PE0</t>
+          <t>PB7</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>IGN2_CTL</t>
+          <t>INJ1_CTL</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>BOOT0</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>BOOT0</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>DFU boot select</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>PB8</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>IGN4_CTL</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>PB9</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>IGN3_CTL</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>PE0</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>IGN2_CTL</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>PE1</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>IGN1_CTL</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr"/>
+      <c r="D58" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/daughterboard/miata_ecu_daughterboard_parts.xlsx
+++ b/daughterboard/miata_ecu_daughterboard_parts.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>C17, C18</t>
+          <t>C16, C17, C18</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2055,27 +2055,27 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>R12, R14</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>C19666</t>
+          <t>C25917</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2086,12 +2086,12 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>CL10A475KO8NNNC</t>
+          <t>0402WGF6801TCE</t>
         </is>
       </c>
     </row>
@@ -2102,27 +2102,27 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>6.8k</t>
+          <t>68k</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>R12, R14</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>C25917</t>
+          <t>C23231</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>0402WGF6801TCE</t>
+          <t>0603WAF6802T5E</t>
         </is>
       </c>
     </row>
@@ -2153,23 +2153,27 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>68k</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr"/>
+          <t>AMS1117-3.3</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>3.3V LDO</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>SOT-223-3_TabPin2</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>C23231</t>
+          <t>C6186</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2180,12 +2184,12 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Advanced Monolithic Systems</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>0603WAF6802T5E</t>
+          <t>AMS1117-3.3</t>
         </is>
       </c>
     </row>
@@ -2196,47 +2200,47 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>AMS1117-3.3</t>
+          <t>B5819W</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>3.3V LDO</t>
+          <t>1A 40V Schottky</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>D8, D10</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>SOT-223-3_TabPin2</t>
+          <t>D_SOD-123</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>C6186</t>
+          <t>C8598</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Advanced Monolithic Systems</t>
+          <t>JSCJ</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>AMS1117-3.3</t>
+          <t>B5819W SL</t>
         </is>
       </c>
     </row>
@@ -2247,31 +2251,31 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>B5819W</t>
+          <t>LMR14020</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>1A 40V Schottky</t>
+          <t>40V 2A buck converter, 12V -&gt; 5V</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>D8, D10</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>D_SOD-123</t>
+          <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.29x3mm</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>C8598</t>
+          <t>C187824</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2282,12 +2286,12 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>JSCJ</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>B5819W SL</t>
+          <t>LMR14020SDDAR</t>
         </is>
       </c>
     </row>
@@ -2302,27 +2306,27 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>LMR14020</t>
+          <t>SMCJ30A</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>40V 2A buck converter, 12V -&gt; 5V</t>
+          <t>1500W TVS, load dump</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.29x3mm</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>C187824</t>
+          <t>C310046</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2333,12 +2337,12 @@
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Brightking</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>LMR14020SDDAR</t>
+          <t>SMCJ30A/TR13</t>
         </is>
       </c>
     </row>
@@ -2353,43 +2357,43 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SMCJ30A</t>
+          <t>SS34</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>1500W TVS, load dump</t>
+          <t>3A 40V Schottky</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>C310046</t>
+          <t>C8678</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Brightking</t>
+          <t>MDD(Microdiode Semiconductor)</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>SMCJ30A/TR13</t>
+          <t>SS34</t>
         </is>
       </c>
     </row>
@@ -2400,21 +2404,17 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SS34</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>3A 40V Schottky</t>
-        </is>
-      </c>
+          <t>SS36</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>D7, D9</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2424,25 +2424,17 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>C8678</t>
+          <t>C7428237</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>MDD(Microdiode Semiconductor)</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>SS34</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2523,39 +2515,43 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr"/>
+          <t>AUIPS2041LTR</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Protected low-side switch, 39V clamp (inj/IACV/VVT/boost/alt)</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>R19, R20, R21, R22, R23, R24, R25, R26</t>
+          <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>SOT-223</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C113610</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Infineon Technologies</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>AUIPS2041LTR</t>
         </is>
       </c>
     </row>
@@ -2566,31 +2562,27 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>AUIPS2041LTR</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Protected low-side switch, 39V clamp (inj/IACV/VVT/boost/alt)</t>
-        </is>
-      </c>
+          <t>VND14NV04</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>Q101</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>SOT-223</t>
+          <t>TO-252-2</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>C113610</t>
+          <t>C2649436</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2601,78 +2593,78 @@
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>AUIPS2041LTR</t>
+          <t>VND14NV04TR-E</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Injector / solenoid drivers</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>VND14NV04</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Q101</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>TO-252-2</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>C2649436</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>STMicroelectronics</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>VND14NV04TR-E</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Ignition drivers</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Ignition drivers</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
+      <c r="B49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>R15, R16, R17, R18</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>C17408</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>0805W8F1000T5E</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -2681,43 +2673,43 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>R15, R16, R17, R18</t>
+          <t>C34, C35</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>C17408</t>
+          <t>C52923</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>0805W8F1000T5E</t>
+          <t>CL05A105KA5NQNC</t>
         </is>
       </c>
     </row>
@@ -2728,43 +2720,43 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>4x10k</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr"/>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>C34, C35</t>
+          <t>RN1</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>R_Array_Convex_4x0603</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>C52923</t>
+          <t>C29718</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>CL05A105KA5NQNC</t>
+          <t>4D03WGJ0103T5E</t>
         </is>
       </c>
     </row>
@@ -2779,39 +2771,43 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4x10k</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr"/>
+          <t>Mezz_Power_Out</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>1x40 2.54mm male header (power/outputs)</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>RN1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>R_Array_Convex_4x0603</t>
+          <t>PinHeader_1x40_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>C29718</t>
+          <t>C2977586</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>ZHOURI</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>4D03WGJ0103T5E</t>
+          <t>2.54-1*40</t>
         </is>
       </c>
     </row>
@@ -2822,31 +2818,31 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mezz_Power_Out</t>
+          <t>TC4427</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>1x40 2.54mm male header (power/outputs)</t>
+          <t>Dual 1.5A driver, 5V logic out for COP smart coils</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>U6, U7</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>PinHeader_1x40_P2.54mm_Vertical</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>C2977586</t>
+          <t>C20551</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2857,150 +2853,146 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>ZHOURI</t>
+          <t>Microchip</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2.54-1*40</t>
+          <t>TC4427AEOA713</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Ignition drivers</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>TC4427</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Dual 1.5A driver, 5V logic out for COP smart coils</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>U6, U7</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>C20551</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>Microchip</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>TC4427AEOA713</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Relay / lamp drivers</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Relay / lamp drivers</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="n"/>
+      <c r="B55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ULN2003AD</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>7ch Darlington low side (relays, CEL, tach)</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>SOIC-16_3.9x9.9mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>C7512</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>ULN2003ADR</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Relay / lamp drivers</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>ULN2003AD</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>7ch Darlington low side (relays, CEL, tach)</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>SOIC-16_3.9x9.9mm_P1.27mm</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>C7512</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Knock input</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Knock input</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>100k</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>R45, R46, R47</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>C25803</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>ULN2003ADR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Knock input</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="n"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>0603WAF1003T5E</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -3009,27 +3001,27 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>R45, R46, R47</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>C25803</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3040,12 +3032,12 @@
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>0603WAF1003T5E</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
     </row>
@@ -3060,23 +3052,23 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3087,12 +3079,12 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
     </row>
@@ -3107,23 +3099,23 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr"/>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>R49</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C57112</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3134,12 +3126,12 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>FH(Guangdong Fenghua Advanced Tech)</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>0603B103K500NT</t>
         </is>
       </c>
     </row>
@@ -3154,13 +3146,13 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr"/>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>C57112</t>
+          <t>C15849</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3181,12 +3173,12 @@
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>FH(Guangdong Fenghua Advanced Tech)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>0603B103K500NT</t>
+          <t>CL10A105KB8NNNC</t>
         </is>
       </c>
     </row>
@@ -3201,23 +3193,23 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr"/>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>C15849</t>
+          <t>C23138</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3228,12 +3220,12 @@
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>CL10A105KB8NNNC</t>
+          <t>0603WAF3300T5E</t>
         </is>
       </c>
     </row>
@@ -3248,13 +3240,13 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3264,7 +3256,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>C23138</t>
+          <t>C25819</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3280,7 +3272,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>0603WAF3300T5E</t>
+          <t>0603WAF4702T5E</t>
         </is>
       </c>
     </row>
@@ -3295,109 +3287,109 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>47k</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
+          <t>LMV321IDBVR</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Op-amp, knock sensor gain stage</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>C25819</t>
+          <t>C7972</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>0603WAF4702T5E</t>
+          <t>LMV321IDBVR</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Knock input</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>VR (crank/cam) input</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>VR (crank/cam) input</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>LMV321IDBVR</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Op-amp, knock sensor gain stage</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>C7972</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>LMV321IDBVR</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>VR (crank/cam) input</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="n"/>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>C50</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>C_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>CC0603KRX7R9BB104</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3406,27 +3398,27 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>R55, R60</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3437,12 +3429,12 @@
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
     </row>
@@ -3457,23 +3449,23 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>R55, R60</t>
+          <t>C48, C49</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C46653</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3484,12 +3476,12 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>CL21B102KBCNNNC</t>
         </is>
       </c>
     </row>
@@ -3500,27 +3492,27 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>C48, C49</t>
+          <t>R51, R52, R53, R54, R56, R57, R58, R59</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>C46653</t>
+          <t>C27834</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3531,12 +3523,12 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>CL21B102KBCNNNC</t>
+          <t>0805W8F5101T5E</t>
         </is>
       </c>
     </row>
@@ -3547,43 +3539,47 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>5.1k</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr"/>
+          <t>MAX9926UAEE+</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Dual VR sensor interface, adaptive threshold</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>R51, R52, R53, R54, R56, R57, R58, R59</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>QSOP-16_3.9x4.9mm_P0.635mm</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>C27834</t>
+          <t>C1523548</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Analog Devices / Maxim Integrated</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>0805W8F5101T5E</t>
+          <t>MAX9926UAEE+</t>
         </is>
       </c>
     </row>
@@ -3598,27 +3594,27 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>MAX9926UAEE+</t>
+          <t>Mezz_Signal_In</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Dual VR sensor interface, adaptive threshold</t>
+          <t>1x40 2.54mm male header (inputs/comms)</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>QSOP-16_3.9x4.9mm_P0.635mm</t>
+          <t>PinHeader_1x40_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>C1523548</t>
+          <t>C2977586</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3629,82 +3625,78 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices / Maxim Integrated</t>
+          <t>ZHOURI</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>MAX9926UAEE+</t>
+          <t>2.54-1*40</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>VR (crank/cam) input</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Mezz_Signal_In</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>1x40 2.54mm male header (inputs/comms)</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>PinHeader_1x40_P2.54mm_Vertical</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>C2977586</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>ZHOURI</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>2.54-1*40</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Analog / hall / switch inputs</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Analog / hall / switch inputs</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
+      <c r="B73" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>R28, R30, R32, R35, R38, R40, R42, R44, R66, R68, R70</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>C25744</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF1002TCE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -3717,23 +3709,23 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr"/>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>R28, R30, R32, R35, R38, R40, R42, R44, R66, R68, R70</t>
+          <t>C36, C37, C38, C39, C40, C41, C42, C43, C53, C54, C55</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C15195</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -3744,12 +3736,12 @@
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>CL05B103KB5NNNC</t>
         </is>
       </c>
     </row>
@@ -3760,45 +3752,37 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>1N4148WS</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr"/>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>C36, C37, C38, C39, C40, C41, C42, C43, C53, C54, C55</t>
+          <t>D13, D14</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>D_SOD-323</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>C15195</t>
+          <t>C2128</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>CL05B103KB5NNNC</t>
-        </is>
-      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -4418,7 +4402,7 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
@@ -4428,7 +4412,7 @@
       <c r="D91" s="5" t="inlineStr"/>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>C111, C112, C113, C114, C116, C102, C105, C108, C109, C118</t>
+          <t>C57, C58, C111, C112, C113, C114, C116, C102, C105, C108, C109, C118</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4475,17 +4459,17 @@
       <c r="D92" s="5" t="inlineStr"/>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>R111, R112, R121, R129, R103, R133, R134, R104</t>
+          <t>R19, R20, R21, R22, R23, R24, R25, R26</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -4501,7 +4485,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
     </row>
@@ -4512,17 +4496,17 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr"/>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>R101, R113, R102, R125, R126, R127, R130</t>
+          <t>R71, R72, R111, R112, R121, R129, R103, R133, R134, R104</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -4532,7 +4516,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -4548,7 +4532,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
     </row>
@@ -4559,32 +4543,32 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>C101, C117, C104, C106, C107</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>C52923</t>
+          <t>C15850</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
@@ -4595,7 +4579,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>CL05A105KA5NQNC</t>
+          <t>CL21A106KAYNNNE</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4590,17 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>22k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R101, R113, R102, R125, R126, R127, R130</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4626,12 +4610,12 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>C25768</t>
+          <t>C11702</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
@@ -4642,7 +4626,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2202TCE</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
     </row>
@@ -4653,27 +4637,27 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>27k</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>R105, R107</t>
+          <t>C101, C117, C104, C106, C107</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>C25771</t>
+          <t>C52923</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -4684,12 +4668,12 @@
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2702TCE</t>
+          <t>CL05A105KA5NQNC</t>
         </is>
       </c>
     </row>
@@ -4704,13 +4688,13 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>3.3k</t>
+          <t>22k</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>R124</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -4720,7 +4704,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>C25890</t>
+          <t>C25768</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -4736,7 +4720,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>0402WGF3301TCE</t>
+          <t>0402WGF2202TCE</t>
         </is>
       </c>
     </row>
@@ -4747,27 +4731,27 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>33n</t>
+          <t>27k</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>R105, R107</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>C285077</t>
+          <t>C25771</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -4778,12 +4762,12 @@
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>0402B333K100NT</t>
+          <t>0402WGF2702TCE</t>
         </is>
       </c>
     </row>
@@ -4798,39 +4782,39 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>3.3k</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>C110</t>
+          <t>R124</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>C19666</t>
+          <t>C25890</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>CL10A475KO8NNNC</t>
+          <t>0402WGF3301TCE</t>
         </is>
       </c>
     </row>
@@ -4845,23 +4829,23 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>33n</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>C25118</t>
+          <t>C285077</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -4872,12 +4856,12 @@
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>0402WGF470JTCE</t>
+          <t>0402B333K100NT</t>
         </is>
       </c>
     </row>
@@ -4892,39 +4876,39 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>47k</t>
+          <t>4.7u</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>C25792</t>
+          <t>C19666</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>0402WGF4702TCE</t>
+          <t>CL10A475KO8NNNC</t>
         </is>
       </c>
     </row>
@@ -4939,13 +4923,13 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>6.8k</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -4955,12 +4939,12 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>C25917</t>
+          <t>C25118</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr"/>
@@ -4971,7 +4955,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>0402WGF6801TCE</t>
+          <t>0402WGF470JTCE</t>
         </is>
       </c>
     </row>
@@ -4986,23 +4970,23 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>C23092</t>
+          <t>C25792</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5018,7 +5002,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>0603WAF619JT5E</t>
+          <t>0402WGF4702TCE</t>
         </is>
       </c>
     </row>
@@ -5033,28 +5017,28 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>62k</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>C23221</t>
+          <t>C25917</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr"/>
@@ -5065,7 +5049,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>0603WAF6202T5E</t>
+          <t>0402WGF6801TCE</t>
         </is>
       </c>
     </row>
@@ -5076,27 +5060,27 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>68k</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>R131, R132</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>C36871</t>
+          <t>C23092</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5112,7 +5096,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>0402WGF6802TCE</t>
+          <t>0603WAF619JT5E</t>
         </is>
       </c>
     </row>
@@ -5127,23 +5111,23 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>AD8628</t>
+          <t>62k</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>U105</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>TSOT-23-5</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C23221</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -5154,12 +5138,12 @@
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>AD8628ARTZ-REEL7</t>
+          <t>0603WAF6202T5E</t>
         </is>
       </c>
     </row>
@@ -5170,27 +5154,27 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>68k</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>R131, R132</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>C2288</t>
+          <t>C36871</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -5201,12 +5185,12 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Hubei KENTO Elec</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>KT-0603B</t>
+          <t>0402WGF6802TCE</t>
         </is>
       </c>
     </row>
@@ -5221,23 +5205,23 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>AD8628</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>U105</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>TSOT-23-5</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>C12624</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -5248,12 +5232,12 @@
       <c r="I108" s="5" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Hubei KENTO Elec</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>KT-0603G</t>
+          <t>AD8628ARTZ-REEL7</t>
         </is>
       </c>
     </row>
@@ -5268,23 +5252,23 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>MCP6004</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>U101</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>C50282</t>
+          <t>C2288</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -5295,12 +5279,12 @@
       <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Microchip</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>MCP6004T-I/ST</t>
+          <t>KT-0603B</t>
         </is>
       </c>
     </row>
@@ -5315,13 +5299,13 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>D101</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -5331,12 +5315,12 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>C2286</t>
+          <t>C12624</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr"/>
@@ -5347,7 +5331,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>KT-0603R</t>
+          <t>KT-0603G</t>
         </is>
       </c>
     </row>
@@ -5362,23 +5346,23 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>REF3033</t>
+          <t>MCP6004</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr"/>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>U103</t>
+          <t>U101</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>C36658</t>
+          <t>C50282</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -5389,12 +5373,12 @@
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microchip</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>REF3033AIDBZR</t>
+          <t>MCP6004T-I/ST</t>
         </is>
       </c>
     </row>
@@ -5409,43 +5393,39 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>3.3V CAN transceiver</t>
-        </is>
-      </c>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>U106</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>C12084</t>
+          <t>C2286</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>KT-0603R</t>
         </is>
       </c>
     </row>
@@ -5460,23 +5440,23 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>STM32F042K6T6</t>
+          <t>REF3033</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>U103</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>LQFP-32_7x7mm_P0.8mm</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>C69216</t>
+          <t>C36658</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -5487,12 +5467,12 @@
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>STM32F042K6T6</t>
+          <t>REF3033AIDBZR</t>
         </is>
       </c>
     </row>
@@ -5503,63 +5483,278 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>SWD (WBO)</t>
+          <t>SMAJ33A</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr"/>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>J102</t>
+          <t>D12, D11</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
-        </is>
-      </c>
-      <c r="G114" s="4" t="inlineStr"/>
-      <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Not assembled</t>
-        </is>
-      </c>
+          <t>D_SMA</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>C3720609</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>SMD1206P050TF/24</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_1206_3216Metric</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>C209741</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr"/>
+    </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>3.3V CAN transceiver</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>U106</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>C12084</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>SN74LVC4245APWR</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>TSSOP-24_4.4x7.8mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>C7859</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>STM32F042K6T6</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>LQFP-32_7x7mm_P0.8mm</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>C69216</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>STM32F042K6T6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>SWD (WBO)</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>J102</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Not assembled</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>Total placements</t>
         </is>
       </c>
-      <c r="B116" s="6">
-        <f>SUMIF(H2:H114,"Basic",B2:B114)+SUMIF(H2:H114,"Extended",B2:B114)</f>
+      <c r="B121" s="6">
+        <f>SUMIF(H2:H119,"Basic",B2:B119)+SUMIF(H2:H119,"Extended",B2:B119)</f>
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>Unique extended parts</t>
         </is>
       </c>
-      <c r="B117" s="6">
-        <f>COUNTIF(H2:H114,"Extended")</f>
+      <c r="B122" s="6">
+        <f>COUNTIF(H2:H119,"Extended")</f>
         <v/>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>JLC charges a one-time loading fee per unique extended part</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>All LCSC numbers were checked against LCSC/JLCPCB listings on 2026-10-28 (manufacturer + MPN columns). Check stock at order time.</t>
         </is>
@@ -6592,7 +6787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6965,607 +7160,639 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>PE7</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>HALL1</t>
+          <t>BOOT1</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>PE8</t>
+          <t>PE7</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>HALL2</t>
+          <t>HALL1</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>PE9</t>
+          <t>PE8</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>HALL2</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>PE10</t>
+          <t>PE9</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>PE11</t>
+          <t>PE10</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SW3</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>PE12</t>
+          <t>PE11</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>VR2_OUT</t>
+          <t>SW3</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>PE13</t>
+          <t>PE12</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>VR1_OUT</t>
+          <t>VR2_OUT</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>PB12</t>
+          <t>PE13</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>CAN_RX</t>
+          <t>VR1_OUT</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>PB13</t>
+          <t>PB12</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>CAN_TX</t>
+          <t>CAN_RX</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>PD8</t>
+          <t>PB13</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>WB_PROG_TX</t>
+          <t>CAN_TX</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>PD9</t>
+          <t>PD8</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>WB_PROG_RX</t>
+          <t>WB_PROG_TX</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>PD10</t>
+          <t>PD9</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>WB_BOOT0</t>
+          <t>WB_PROG_RX</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>PD11</t>
+          <t>PD10</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>WB_NRST</t>
+          <t>WB_BOOT0</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>PD12</t>
+          <t>PD11</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>LED_RUN</t>
+          <t>WB_NRST</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>PD13</t>
+          <t>PD12</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>LED_COMM</t>
+          <t>LED_RUN</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>PD14</t>
+          <t>PD13</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>LED_WARN</t>
+          <t>LED_COMM</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>PD15</t>
+          <t>PD14</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>LED_ERR</t>
+          <t>LED_WARN</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PD15</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>UART_TX</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>USART3 TX (3.3V, Bluetooth etc.)</t>
-        </is>
-      </c>
+          <t>LED_ERR</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>UART_RX</t>
+          <t>UART_TX</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>USART3 RX</t>
+          <t>USART3 TX (3.3V, Bluetooth etc.)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>PA11</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>USB_DM</t>
+          <t>UART_RX</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>USB D- to motherboard USB-C</t>
+          <t>USART3 RX</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>PA12</t>
+          <t>PA8</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>USB_DP</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>USB D+</t>
-        </is>
-      </c>
+          <t>DRV_EN_N</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PA13</t>
+          <t>PA11</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>SWDIO</t>
+          <t>USB_DM</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>SWD data</t>
+          <t>USB D- to motherboard USB-C</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>PA14</t>
+          <t>PA12</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>SWCLK</t>
+          <t>USB_DP</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>SWD clock</t>
+          <t>USB D+</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>PD5</t>
+          <t>PA13</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>ALT_CTL</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr"/>
+          <t>SWDIO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>SWD data</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>PD6</t>
+          <t>PA14</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>BOOST_CTL</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr"/>
+          <t>SWCLK</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>SWD clock</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>PD7</t>
+          <t>PD5</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>VVT_CTL</t>
+          <t>ALT_CTL</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>PB3</t>
+          <t>PD6</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>IACV_CTL</t>
+          <t>BOOST_CTL</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PD7</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>INJ4_CTL</t>
+          <t>VVT_CTL</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>PB5</t>
+          <t>PB3</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>INJ3_CTL</t>
+          <t>IACV_CTL</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>PB6</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>INJ2_CTL</t>
+          <t>INJ4_CTL</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>PB7</t>
+          <t>PB5</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>INJ1_CTL</t>
+          <t>INJ3_CTL</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>BOOT0</t>
+          <t>PB6</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>BOOT0</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>DFU boot select</t>
-        </is>
-      </c>
+          <t>INJ2_CTL</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>PB8</t>
+          <t>PB7</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>IGN4_CTL</t>
+          <t>INJ1_CTL</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>PB9</t>
+          <t>BOOT0</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>IGN3_CTL</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr"/>
+          <t>BOOT0</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>DFU boot select</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>PE0</t>
+          <t>PB8</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>IGN2_CTL</t>
+          <t>IGN4_CTL</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>PB9</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>IGN3_CTL</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>PE0</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>IGN2_CTL</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>PE1</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>IGN1_CTL</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr"/>
+      <c r="D60" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/daughterboard/miata_ecu_daughterboard_parts.xlsx
+++ b/daughterboard/miata_ecu_daughterboard_parts.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>22p</t>
+          <t>33p</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>C1653</t>
+          <t>C1663</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>CL10C220JB8NNNC</t>
+          <t>CL10C330JB8NNNC</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>L_Sunlord_MWSA0503S</t>
+          <t>L_Sunlord_MWSA0603S</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>C139506</t>
+          <t>C132141</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>MWSA0503-100MT</t>
+          <t>MWSA0603S-100MT</t>
         </is>
       </c>
     </row>
@@ -2433,8 +2433,16 @@
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>SS36(SMA)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3781,8 +3789,16 @@
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>JSCJ</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>1N4148WS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -5512,8 +5528,16 @@
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>BOURNS</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>SMAJ33A</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -5551,8 +5575,16 @@
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="4" t="inlineStr"/>
-      <c r="K115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>PTTC(Polytronics Tech)</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>SMD1206P050TF/24</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -5641,8 +5673,16 @@
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
-      <c r="K117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>SN74LVC4245APWR</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">

--- a/daughterboard/miata_ecu_daughterboard_parts.xlsx
+++ b/daughterboard/miata_ecu_daughterboard_parts.xlsx
@@ -1259,23 +1259,23 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>C72041</t>
+          <t>C2288</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>EVERLIGHT</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>19-217/BHC-ZL1M2RY/3T</t>
+          <t>KT-0603B</t>
         </is>
       </c>
     </row>
@@ -1306,23 +1306,23 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>C72043</t>
+          <t>C12624</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>EVERLIGHT</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>19-217/GHC-YR1S2/3T</t>
+          <t>KT-0603G</t>
         </is>
       </c>
     </row>
@@ -1400,23 +1400,23 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>C72038</t>
+          <t>C2287</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>EVERLIGHT</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>19-213/Y2C-CQ2R2L/3T(CY)</t>
+          <t>KT-0603Y</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>C223413</t>
+          <t>C70960</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1945,12 +1945,12 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Taiyo Yuden</t>
+          <t>FH(Guangdong Fenghua Advanced Tech)</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>LBC3225T2R2MR</t>
+          <t>CMI322513U2R2KT</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>AUIPS2041LTR</t>
+          <t>NCV8406ASTT3G</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Protected low-side switch, 39V clamp (inj/IACV/VVT/boost/alt)</t>
+          <t>Self-protected low-side driver, 60-70V clamp (inj/IACV/VVT/boost/alt)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>C113610</t>
+          <t>C459816</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2554,12 +2554,12 @@
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>AUIPS2041LTR</t>
+          <t>NCV8406ASTT3G</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>C285077</t>
+          <t>C106862</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -4872,12 +4872,12 @@
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>0402B333K100NT</t>
+          <t>CC0402KRX7R9BB333</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>C23092</t>
+          <t>C23222</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>0603WAF619JT5E</t>
+          <t>0603WAF620JT5E</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>TSOT-23-5</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>C3720609</t>
+          <t>C223988</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -5530,7 +5530,7 @@
       <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>BOURNS</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
@@ -5550,23 +5550,27 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>SMD1206P050TF/24</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr"/>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>3.3V CAN transceiver</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>U106</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Fuse_1206_3216Metric</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>C209741</t>
+          <t>C12084</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -5577,12 +5581,12 @@
       <c r="I115" s="5" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>PTTC(Polytronics Tech)</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>SMD1206P050TF/24</t>
+          <t>SN65HVD230DR</t>
         </is>
       </c>
     </row>
@@ -5597,27 +5601,23 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>3.3V CAN transceiver</t>
-        </is>
-      </c>
+          <t>SN74LVC4245APWR</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>U106</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>TSSOP-24_4.4x7.8mm_P0.65mm</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>C12084</t>
+          <t>C7859</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>SN74LVC4245APWR</t>
         </is>
       </c>
     </row>
@@ -5648,23 +5648,23 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>SN74LVC4245APWR</t>
+          <t>STM32F042K6T6</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U102</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>TSSOP-24_4.4x7.8mm_P0.65mm</t>
+          <t>LQFP-32_7x7mm_P0.8mm</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>C7859</t>
+          <t>C69216</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -5675,12 +5675,12 @@
       <c r="I117" s="5" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>SN74LVC4245APWR</t>
+          <t>STM32F042K6T6</t>
         </is>
       </c>
     </row>
@@ -5695,41 +5695,29 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>STM32F042K6T6</t>
+          <t>SWD (WBO)</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>J102</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>LQFP-32_7x7mm_P0.8mm</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>C69216</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
-      <c r="I118" s="5" t="inlineStr"/>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>STMicroelectronics</t>
-        </is>
-      </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>STM32F042K6T6</t>
-        </is>
-      </c>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Not assembled</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -5742,29 +5730,41 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SWD (WBO)</t>
+          <t>nSMD050-33V</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>J102</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr"/>
-      <c r="H119" s="4" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Not assembled</t>
-        </is>
-      </c>
-      <c r="J119" s="4" t="inlineStr"/>
-      <c r="K119" s="4" t="inlineStr"/>
+          <t>Fuse_1206_3216Metric</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>C70077</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>TECHFUSE</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>nSMD050-33V</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">

--- a/daughterboard/miata_ecu_daughterboard_parts.xlsx
+++ b/daughterboard/miata_ecu_daughterboard_parts.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2200,31 +2200,31 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>B5819W</t>
+          <t>B360A</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>1A 40V Schottky</t>
+          <t>3A 60V Schottky, buck catch diode</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>D8, D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>D_SOD-123</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>C8598</t>
+          <t>C94193</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2235,12 +2235,12 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>JSCJ</t>
+          <t>Diodes Incorporated</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>B5819W SL</t>
+          <t>B360A-13-F</t>
         </is>
       </c>
     </row>
@@ -2251,31 +2251,31 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>LMR14020</t>
+          <t>B5819W</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>40V 2A buck converter, 12V -&gt; 5V</t>
+          <t>1A 40V Schottky</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>D8, D10</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.29x3mm</t>
+          <t>D_SOD-123</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>C187824</t>
+          <t>C8598</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2286,12 +2286,12 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>JSCJ</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>LMR14020SDDAR</t>
+          <t>B5819W SL</t>
         </is>
       </c>
     </row>
@@ -2306,27 +2306,27 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SMCJ30A</t>
+          <t>LMR14020</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>1500W TVS, load dump</t>
+          <t>40V 2A buck converter, 12V -&gt; 5V</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.29x3mm</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>C310046</t>
+          <t>C187824</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Brightking</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>SMCJ30A/TR13</t>
+          <t>LMR14020SDDAR</t>
         </is>
       </c>
     </row>
@@ -2357,43 +2357,43 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SS34</t>
+          <t>SMCJ30A</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>3A 40V Schottky</t>
+          <t>1500W TVS, load dump</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>C8678</t>
+          <t>C224048</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>MDD(Microdiode Semiconductor)</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>SS34</t>
+          <t>SMCJ30A</t>
         </is>
       </c>
     </row>
@@ -2408,13 +2408,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SS36</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr"/>
+          <t>SS34</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>3A 40V Schottky</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2424,23 +2428,23 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>C7428237</t>
+          <t>C8678</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>MDD(Microdiode Semiconductor)</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>SS36(SMA)</t>
+          <t>SS34</t>
         </is>
       </c>
     </row>
@@ -3359,43 +3363,43 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>R73, R74, R75, R76</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
     </row>
@@ -3406,27 +3410,27 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>R55, R60</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C1525</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3437,12 +3441,12 @@
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>CL05B104KO5NNNC</t>
         </is>
       </c>
     </row>
@@ -3453,27 +3457,27 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>C48, C49</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>C46653</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3484,12 +3488,12 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>CL21B102KBCNNNC</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
     </row>
@@ -3500,27 +3504,27 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>5.1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>R51, R52, R53, R54, R56, R57, R58, R59</t>
+          <t>R79, R80</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>C27834</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3536,7 +3540,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>0805W8F5101T5E</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
     </row>
@@ -3547,47 +3551,43 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>MAX9926UAEE+</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Dual VR sensor interface, adaptive threshold</t>
-        </is>
-      </c>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>R55, R60</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>QSOP-16_3.9x4.9mm_P0.635mm</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>C1523548</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices / Maxim Integrated</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>MAX9926UAEE+</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
     </row>
@@ -3598,31 +3598,27 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Mezz_Signal_In</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>1x40 2.54mm male header (inputs/comms)</t>
-        </is>
-      </c>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>R77, R78</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>PinHeader_1x40_P2.54mm_Vertical</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>C2977586</t>
+          <t>C26083</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3633,60 +3629,90 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>ZHOURI</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2.54-1*40</t>
+          <t>0402WGF1004TCE</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Analog / hall / switch inputs</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="n"/>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>VR (crank/cam) input</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>1n</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>C48, C49</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>C46653</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Electro-Mechanics</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>CL21B102KBCNNNC</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Analog / hall / switch inputs</t>
+          <t>VR (crank/cam) input</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>5.1k</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>R28, R30, R32, R35, R38, R40, R42, R44, R66, R68, R70</t>
+          <t>R51, R52, R53, R54, R56, R57, R58, R59</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C27834</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3702,85 +3728,93 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0805W8F5101T5E</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Analog / hall / switch inputs</t>
+          <t>VR (crank/cam) input</t>
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>10n</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
+          <t>BAT54S</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Dual series Schottky, VR input clamp</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>C36, C37, C38, C39, C40, C41, C42, C43, C53, C54, C55</t>
+          <t>D15, D16, D17, D18</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>C15195</t>
+          <t>C19726</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>CL05B103KB5NNNC</t>
+          <t>BAT54SLT1G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Analog / hall / switch inputs</t>
+          <t>VR (crank/cam) input</t>
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1N4148WS</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr"/>
+          <t>LM2903DR</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Dual comparator, VR input conditioner (spare VR inputs)</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>D13, D14</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>D_SOD-323</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>C2128</t>
+          <t>C7549</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -3791,108 +3825,82 @@
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>JSCJ</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>1N4148WS</t>
+          <t>LM2903DR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Analog / hall / switch inputs</t>
+          <t>VR (crank/cam) input</t>
         </is>
       </c>
       <c r="B76" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr"/>
+          <t>Mezz_Signal_In</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>1x40 2.54mm male header (inputs/comms)</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>R62, R64</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>PinHeader_1x40_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C2977586</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>ZHOURI</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>2.54-1*40</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Analog / hall / switch inputs</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>1n</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>C51, C52</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>C_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>C1523</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>FH(Guangdong Fenghua Advanced Tech)</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>0402B102K500NT</t>
-        </is>
-      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3901,17 +3909,17 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>2.7k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr"/>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>R33, R36</t>
+          <t>R28, R30, R32, R35, R38, R40, R42, R44, R66, R68, R70</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3921,23 +3929,23 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>C25885</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2701TCE</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
     </row>
@@ -3948,27 +3956,27 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>33k</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>R65, R67, R69</t>
+          <t>C36, C37, C38, C39, C40, C41, C42, C43, C53, C54, C55</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>C25779</t>
+          <t>C15195</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -3979,12 +3987,12 @@
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>0402WGF3302TCE</t>
+          <t>CL05B103KB5NNNC</t>
         </is>
       </c>
     </row>
@@ -3999,39 +4007,39 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>1N4148WS</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr"/>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>R61, R63</t>
+          <t>D13, D14</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>D_SOD-323</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>C25900</t>
+          <t>C2128</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>JSCJ</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>0402WGF4701TCE</t>
+          <t>1N4148WS</t>
         </is>
       </c>
     </row>
@@ -4042,17 +4050,17 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>5.6k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr"/>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>R27, R29, R31, R34, R37, R39, R41, R43</t>
+          <t>R62, R64</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4062,7 +4070,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>C25908</t>
+          <t>C11702</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4078,185 +4086,249 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>0402WGF5601TCE</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="3" t="n"/>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="3" t="n"/>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Analog / hall / switch inputs</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>1n</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>C51, C52</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>C_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>C1523</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>FH(Guangdong Fenghua Advanced Tech)</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>0402B102K500NT</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>Analog / hall / switch inputs</t>
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>2.7k</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr"/>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>R33, R36</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C25885</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>0402WGF2701TCE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>Analog / hall / switch inputs</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>3.3V CAN transceiver</t>
-        </is>
-      </c>
+          <t>33k</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>R65, R67, R69</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>C12084</t>
+          <t>C25779</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>0402WGF3302TCE</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="3" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="n"/>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Analog / hall / switch inputs</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>4.7k</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>R61, R63</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>C25900</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF4701TCE</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Analog / hall / switch inputs</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>M3 mounting hole</t>
-        </is>
-      </c>
+          <t>5.6k</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr"/>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>H1, H2, H3, H4</t>
+          <t>R27, R29, R31, R34, R37, R39, R41, R43</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>MountingHole_3.2mm_M3</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Not assembled</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
+          <t>R_0402_1005Metric</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>C25908</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>0402WGF5601TCE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B87" s="3" t="n"/>
@@ -4273,7 +4345,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B88" s="4" t="n">
@@ -4281,70 +4353,74 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr"/>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>C25077</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>0402WGF100JTCE</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>100k</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr"/>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>3.3V CAN transceiver</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>R115, R117, R120</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>C25741</t>
+          <t>C12084</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4355,155 +4431,87 @@
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1003TCE</t>
+          <t>SN65HVD230DR</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>100n</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr"/>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>C47</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>C_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>C14663</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>YAGEO</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>CC0603KRX7R9BB104</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>M3 mounting hole</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>H1, H2, H3, H4</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>MountingHole_3.2mm_M3</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Not assembled</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>100n</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr"/>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>C57, C58, C111, C112, C113, C114, C116, C102, C105, C108, C109, C118</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>C_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>C1525</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>Samsung Electro-Mechanics</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>CL05B104KO5NNNC</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>R19, R20, R21, R22, R23, R24, R25, R26</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>C25804</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>0603WAF1002T5E</t>
-        </is>
-      </c>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -4512,17 +4520,17 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr"/>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>R71, R72, R111, R112, R121, R129, R103, R133, R134, R104</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -4532,12 +4540,12 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25077</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
@@ -4548,7 +4556,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0402WGF100JTCE</t>
         </is>
       </c>
     </row>
@@ -4559,43 +4567,43 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr"/>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>R115, R117, R120</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>C15850</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>CL21A106KAYNNNE</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
     </row>
@@ -4606,27 +4614,27 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>R101, R113, R102, R125, R126, R127, R130</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -4637,12 +4645,12 @@
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
     </row>
@@ -4653,17 +4661,17 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr"/>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>C101, C117, C104, C106, C107</t>
+          <t>C57, C58, C111, C112, C113, C114, C116, C102, C105, C108, C109, C118</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -4673,12 +4681,12 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>C52923</t>
+          <t>C1525</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr"/>
@@ -4689,7 +4697,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>CL05A105KA5NQNC</t>
+          <t>CL05B104KO5NNNC</t>
         </is>
       </c>
     </row>
@@ -4700,32 +4708,32 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>22k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R19, R20, R21, R22, R23, R24, R25, R26</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>C25768</t>
+          <t>C25804</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr"/>
@@ -4736,7 +4744,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2202TCE</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
     </row>
@@ -4747,17 +4755,17 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>27k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr"/>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>R105, R107</t>
+          <t>R71, R72, R111, R112, R121, R129, R103, R133, R134, R104</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -4767,12 +4775,12 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>C25771</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr"/>
@@ -4783,7 +4791,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>0402WGF2702TCE</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
     </row>
@@ -4798,39 +4806,39 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>3.3k</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>R124</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>C25890</t>
+          <t>C15850</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>0402WGF3301TCE</t>
+          <t>CL21A106KAYNNNE</t>
         </is>
       </c>
     </row>
@@ -4841,43 +4849,43 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>33n</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>R101, R113, R102, R125, R126, R127, R130</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>C106862</t>
+          <t>C11702</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>CC0402KRX7R9BB333</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
     </row>
@@ -4888,32 +4896,32 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>C110</t>
+          <t>C101, C117, C104, C106, C107</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>C19666</t>
+          <t>C52923</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr"/>
@@ -4924,7 +4932,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>CL10A475KO8NNNC</t>
+          <t>CL05A105KA5NQNC</t>
         </is>
       </c>
     </row>
@@ -4939,13 +4947,13 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>22k</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -4955,7 +4963,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>C25118</t>
+          <t>C25768</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -4971,7 +4979,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>0402WGF470JTCE</t>
+          <t>0402WGF2202TCE</t>
         </is>
       </c>
     </row>
@@ -4982,17 +4990,17 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>47k</t>
+          <t>27k</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R105, R107</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -5002,7 +5010,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>C25792</t>
+          <t>C25771</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5018,7 +5026,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>0402WGF4702TCE</t>
+          <t>0402WGF2702TCE</t>
         </is>
       </c>
     </row>
@@ -5033,13 +5041,13 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>6.8k</t>
+          <t>3.3k</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R124</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -5049,12 +5057,12 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>C25917</t>
+          <t>C25890</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr"/>
@@ -5065,7 +5073,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>0402WGF6801TCE</t>
+          <t>0402WGF3301TCE</t>
         </is>
       </c>
     </row>
@@ -5080,23 +5088,23 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>33n</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>C23222</t>
+          <t>C106862</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5107,12 +5115,12 @@
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>0603WAF620JT5E</t>
+          <t>CC0402KRX7R9BB333</t>
         </is>
       </c>
     </row>
@@ -5127,39 +5135,39 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>62k</t>
+          <t>4.7u</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>C23221</t>
+          <t>C19666</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>UNI-ROYAL(Uniroyal Elec)</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>0603WAF6202T5E</t>
+          <t>CL10A475KO8NNNC</t>
         </is>
       </c>
     </row>
@@ -5170,17 +5178,17 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>68k</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>R131, R132</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -5190,7 +5198,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>C36871</t>
+          <t>C25118</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -5206,7 +5214,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>0402WGF6802TCE</t>
+          <t>0402WGF470JTCE</t>
         </is>
       </c>
     </row>
@@ -5221,23 +5229,23 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>AD8628</t>
+          <t>47k</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>U105</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C25792</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -5248,12 +5256,12 @@
       <c r="I108" s="5" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>AD8628ARTZ-REEL7</t>
+          <t>0402WGF4702TCE</t>
         </is>
       </c>
     </row>
@@ -5268,39 +5276,39 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>C2288</t>
+          <t>C25917</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Hubei KENTO Elec</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>KT-0603B</t>
+          <t>0402WGF6801TCE</t>
         </is>
       </c>
     </row>
@@ -5315,23 +5323,23 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>C12624</t>
+          <t>C23222</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -5342,12 +5350,12 @@
       <c r="I110" s="5" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Hubei KENTO Elec</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>KT-0603G</t>
+          <t>0603WAF620JT5E</t>
         </is>
       </c>
     </row>
@@ -5362,23 +5370,23 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>MCP6004</t>
+          <t>62k</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr"/>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>U101</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>C50282</t>
+          <t>C23221</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -5389,12 +5397,12 @@
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Microchip</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>MCP6004T-I/ST</t>
+          <t>0603WAF6202T5E</t>
         </is>
       </c>
     </row>
@@ -5405,43 +5413,43 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>68k</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr"/>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>D101</t>
+          <t>R131, R132</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>C2286</t>
+          <t>C36871</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Hubei KENTO Elec</t>
+          <t>UNI-ROYAL(Uniroyal Elec)</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>KT-0603R</t>
+          <t>0402WGF6802TCE</t>
         </is>
       </c>
     </row>
@@ -5456,23 +5464,23 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>REF3033</t>
+          <t>AD8628</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>U103</t>
+          <t>U105</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>C36658</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -5483,12 +5491,12 @@
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>REF3033AIDBZR</t>
+          <t>AD8628ARTZ-REEL7</t>
         </is>
       </c>
     </row>
@@ -5499,27 +5507,27 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>SMAJ33A</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr"/>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>D12, D11</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>C223988</t>
+          <t>C2288</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -5530,12 +5538,12 @@
       <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>SMAJ33A</t>
+          <t>KT-0603B</t>
         </is>
       </c>
     </row>
@@ -5550,27 +5558,23 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>3.3V CAN transceiver</t>
-        </is>
-      </c>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>U106</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>C12084</t>
+          <t>C12624</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -5581,12 +5585,12 @@
       <c r="I115" s="5" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>KT-0603G</t>
         </is>
       </c>
     </row>
@@ -5601,23 +5605,23 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>SN74LVC4245APWR</t>
+          <t>MCP6004</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U101</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>TSSOP-24_4.4x7.8mm_P0.65mm</t>
+          <t>TSSOP-14_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>C7859</t>
+          <t>C50282</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -5628,12 +5632,12 @@
       <c r="I116" s="5" t="inlineStr"/>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microchip</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>SN74LVC4245APWR</t>
+          <t>MCP6004T-I/ST</t>
         </is>
       </c>
     </row>
@@ -5648,39 +5652,39 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>STM32F042K6T6</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>LQFP-32_7x7mm_P0.8mm</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>C69216</t>
+          <t>C2286</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Hubei KENTO Elec</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>STM32F042K6T6</t>
+          <t>KT-0603R</t>
         </is>
       </c>
     </row>
@@ -5695,29 +5699,41 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>SWD (WBO)</t>
+          <t>REF3033</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>J102</t>
+          <t>U103</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr"/>
-      <c r="H118" s="4" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>Not assembled</t>
-        </is>
-      </c>
-      <c r="J118" s="4" t="inlineStr"/>
-      <c r="K118" s="4" t="inlineStr"/>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>C36658</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>REF3033AIDBZR</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -5726,27 +5742,27 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>nSMD050-33V</t>
+          <t>SMAJ33A</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>D12, D11</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Fuse_1206_3216Metric</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>C70077</t>
+          <t>C223988</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -5757,44 +5773,271 @@
       <c r="I119" s="5" t="inlineStr"/>
       <c r="J119" s="4" t="inlineStr">
         <is>
+          <t>Littelfuse</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>SMAJ33A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>3.3V CAN transceiver</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>U106</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>C12084</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>SN65HVD230DR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>SN74LVC4245APWR</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>TSSOP-24_4.4x7.8mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>C7859</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>SN74LVC4245APWR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>STM32F042K6T6</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>LQFP-32_7x7mm_P0.8mm</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>C69216</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>STM32F042K6T6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>SWD (WBO)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>J102</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Not assembled</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>nSMD050-33V</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Fuse_1206_3216Metric</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>C70077</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
           <t>TECHFUSE</t>
         </is>
       </c>
-      <c r="K119" s="4" t="inlineStr">
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>nSMD050-33V</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>Total placements</t>
         </is>
       </c>
-      <c r="B121" s="6">
-        <f>SUMIF(H2:H119,"Basic",B2:B119)+SUMIF(H2:H119,"Extended",B2:B119)</f>
+      <c r="B126" s="6">
+        <f>SUMIF(H2:H124,"Basic",B2:B124)+SUMIF(H2:H124,"Extended",B2:B124)</f>
         <v/>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Unique extended parts</t>
         </is>
       </c>
-      <c r="B122" s="6">
-        <f>COUNTIF(H2:H119,"Extended")</f>
+      <c r="B127" s="6">
+        <f>COUNTIF(H2:H124,"Extended")</f>
         <v/>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>JLC charges a one-time loading fee per unique extended part</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>All LCSC numbers were checked against LCSC/JLCPCB listings on 2026-10-28 (manufacturer + MPN columns). Check stock at order time.</t>
         </is>
